--- a/templates/Templat-Impor-Siswa.xlsx
+++ b/templates/Templat-Impor-Siswa.xlsx
@@ -219,7 +219,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Mis. X TJKT 1. Dipakai untuk mendaftarkan satu kelas sekaligus ke kursus.</t>
+        <t>Mis. X TJKT 1. Dipakai untuk mendaftarkan satu kelas sekaligus ke mata pelajaran.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
@@ -239,7 +239,7 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>siswa / guru / admin. Kosong = siswa. (Diabaikan saat guru mengimpor ke kursus.)</t>
+        <t>siswa / guru / admin. Kosong = siswa. (Diabaikan saat guru mengimpor ke mapel.)</t>
       </text>
     </comment>
   </commentList>
@@ -4260,14 +4260,14 @@
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>5.  Baris dengan username yang sudah terdaftar akan dilewati (admin) atau langsung didaftarkan ke kursus (impor dari halaman Peserta).</t>
+          <t>5.  Baris dengan username yang sudah terdaftar akan dilewati (admin) atau langsung didaftarkan ke mata pelajaran (impor dari halaman Peserta).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>6.  Simpan sebagai .xlsx, lalu unggah di LMS: Administrasi Situs → Pengguna → Impor, atau di kursus: Peserta → Impor Excel.</t>
+          <t>6.  Simpan sebagai .xlsx, lalu unggah di LMS: Administrasi Situs → Pengguna → Impor, atau di halaman Mapel: Peserta → Impor Excel.</t>
         </is>
       </c>
     </row>
